--- a/vse-loti/339548308/spec-339548308.xlsx
+++ b/vse-loti/339548308/spec-339548308.xlsx
@@ -506,6 +506,16 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1867693</v>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>

--- a/vse-loti/339548308/spec-339548308.xlsx
+++ b/vse-loti/339548308/spec-339548308.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +437,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,7 +505,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -512,7 +515,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>1867693</v>
       </c>
     </row>

--- a/vse-loti/339548308/spec-339548308.xlsx
+++ b/vse-loti/339548308/spec-339548308.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -60,13 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -500,29 +504,520 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Муфта электросварная ПНД 315 SDR 11 ПЭ 100</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>11333.33</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>13600</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>67999.98</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Муфта электросварная ПНД 500 SDR 11 ПЭ 100</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>29166.67</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>175000.02</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Отвод сварной сегментированный ПНД 315 90гр SDR 11 ПЭ 100</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="3" t="n">
+        <v>15166.67</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>18200</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>30333.34</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Отвод сварной сегментированный ПНД 500 90гр SDR 11 ПЭ 100</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="3" t="n">
+        <v>24666.67</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>29600</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>49333.34</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Труба ПНД 110 SDR 13.6 ПЭ 100 ГОСТ 18599-2001 питьевая вода в бухтах</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>71334</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Труба ПНД 315 SDR 13.6 ПЭ 100 ГОСТ 18599-2001 питьевая вода в отрезках 12 метров</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>4033.33</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>4840</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>145199.88</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Труба ПНД 32 SDR 17 ПЭ 100 ГОСТ 18599-2001 питьевая вода в бухтах</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>123.33</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>24666</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>425275.86</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>510331.03</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Труба ПНД 40 SDR 17 ПЭ 100 ГОСТ 18599-2001 питьевая вода в бухтах</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>48859.93</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>58631.92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Труба ПНД 400 SDR 13.6 ПЭ 100 ГОСТ 18599-2001 питьевая вода в отрезках 12 метров</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="3" t="n">
+        <v>6900</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>8280</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>82800</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Труба ПНД 50 SDR 17 ПЭ 100 ГОСТ 18599-2001 питьевая вода в бухтах</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>181.33</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>217.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>36266</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>47098.7</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>56518.44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Труба ПНД 500 SDR 13.6 ПЭ 100 ГОСТ 18599-2001 питьевая вода в отрезках 12 метров</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="3" t="n">
+        <v>11500</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>552000</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Труба ПНД 63 SDR 17 ПЭ 100 ГОСТ 18599-2001 питьевая вода в бухтах</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>43000</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Труба ПНД 75 SDR 13.6 ПЭ 100 ГОСТ 18599-2001 питьевая вода в бухтах</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Труба гофрированная полиэтиленовая DN /ОD 160*136</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="3" t="n">
+        <v>856.67</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1028</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>257001</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Труба гофрированная полиэтиленовая DN/OD 200*171</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="3" t="n">
+        <v>1713.33</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>2056</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>174759.66</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Труба гофрированная полиэтиленовая DN/ID 225*200, трубы по 6 метров</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="3" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>12360</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>103000</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>1867693</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Источник: 852909901.doc</t>
+      <c r="E18" s="5" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1867693.22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Источник: 852909900.txt</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339548308/spec-339548308.xlsx
+++ b/vse-loti/339548308/spec-339548308.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -61,16 +61,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,8 +448,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -522,16 +511,10 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>11333.33</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>13600</v>
-      </c>
-      <c r="H2" s="3" t="n">
         <v>67999.98</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -552,16 +535,10 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>29166.67</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>35000</v>
-      </c>
-      <c r="H3" s="3" t="n">
         <v>175000.02</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -582,16 +559,10 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>15166.67</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>18200</v>
-      </c>
-      <c r="H4" s="3" t="n">
         <v>30333.34</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -612,16 +583,10 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" s="3" t="n">
-        <v>24666.67</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>29600</v>
-      </c>
-      <c r="H5" s="3" t="n">
         <v>49333.34</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -640,18 +605,18 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" s="4" t="n">
+        <v>0.493</v>
+      </c>
       <c r="F6" s="3" t="n">
-        <v>356.67</v>
+        <v>71334</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>428</v>
+        <v>144787.69</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>71334</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>173745.23</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -670,18 +635,18 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="4" t="n">
+        <v>0.727</v>
+      </c>
       <c r="F7" s="3" t="n">
-        <v>4033.33</v>
+        <v>145199.88</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4840</v>
+        <v>199626.32</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>145199.88</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+        <v>239551.58</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -700,23 +665,17 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>0.058</v>
+      <c r="E8" s="4" t="n">
+        <v>0.034</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>123.33</v>
+        <v>24666</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>148</v>
+        <v>722495.61</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>24666</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>425275.86</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>510331.03</v>
+        <v>866994.73</v>
       </c>
     </row>
     <row r="9">
@@ -736,23 +695,17 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0.614</v>
+      <c r="E9" s="4" t="n">
+        <v>0.054</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>150</v>
+        <v>30000</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>180</v>
+        <v>556999.63</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>48859.93</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>58631.92</v>
+        <v>668399.55</v>
       </c>
     </row>
     <row r="10">
@@ -772,18 +725,18 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="4" t="n">
+        <v>0.39</v>
+      </c>
       <c r="F10" s="3" t="n">
-        <v>6900</v>
+        <v>82800</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8280</v>
+        <v>212188.87</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>82800</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>254626.64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -802,23 +755,17 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0.77</v>
+      <c r="E11" s="4" t="n">
+        <v>0.082</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>181.33</v>
+        <v>36266</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>217.6</v>
+        <v>444763.31</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>36266</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>47098.7</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>56518.44</v>
+        <v>533715.97</v>
       </c>
     </row>
     <row r="12">
@@ -838,18 +785,18 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" s="4" t="n">
+        <v>2.442</v>
+      </c>
       <c r="F12" s="3" t="n">
-        <v>11500</v>
+        <v>552000</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>13800</v>
+        <v>226051.78</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>552000</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>271262.14</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -868,18 +815,18 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" s="4" t="n">
+        <v>0.131</v>
+      </c>
       <c r="F13" s="3" t="n">
-        <v>215</v>
+        <v>43000</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>258</v>
+        <v>328344.53</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>43000</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>394013.44</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -898,18 +845,18 @@
           <t>м</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" s="4" t="n">
+        <v>0.114</v>
+      </c>
       <c r="F14" s="3" t="n">
-        <v>250</v>
+        <v>25000</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>300</v>
+        <v>219144.46</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+        <v>262973.35</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -930,16 +877,10 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="3" t="n">
-        <v>856.67</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>1028</v>
-      </c>
-      <c r="H15" s="3" t="n">
         <v>257001</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -960,16 +901,10 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="3" t="n">
-        <v>1713.33</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>2056</v>
-      </c>
-      <c r="H16" s="3" t="n">
         <v>174759.66</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -990,28 +925,32 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" s="3" t="n">
-        <v>10300</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>12360</v>
-      </c>
-      <c r="H17" s="3" t="n">
         <v>103000</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1.442</v>
-      </c>
-      <c r="H18" s="6" t="n">
+      <c r="E18" s="6" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F18" s="7" t="n">
         <v>1867693.22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>560308</v>
       </c>
     </row>
     <row r="21">
